--- a/core_portfolio.xlsx
+++ b/core_portfolio.xlsx
@@ -1,34 +1,67 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daivieth/Documents/_G8I/Development/IVP-Portfolio-Management-Utils/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2020A5F9-F7E2-9C44-8F7E-77ACACA086BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="15300" windowHeight="19760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>ticker</t>
+  </si>
+  <si>
+    <t>quantity</t>
+  </si>
+  <si>
+    <t>SLF.AX</t>
+  </si>
+  <si>
+    <t>ROYL.AX</t>
+  </si>
+  <si>
+    <t>UMAX.AX</t>
+  </si>
+  <si>
+    <t>YMAX.AX</t>
+  </si>
+  <si>
+    <t>VHY.AX</t>
+  </si>
+  <si>
+    <t>XGOV.AX</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,81 +79,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,54 +383,64 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>TLT</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>50</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1">
+        <v>750</v>
       </c>
     </row>
   </sheetData>

--- a/core_portfolio.xlsx
+++ b/core_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daivieth/Documents/_G8I/Development/IVP-Portfolio-Management-Utils/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2020A5F9-F7E2-9C44-8F7E-77ACACA086BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F60BE52-A41A-444E-8711-454209F3CAB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="15300" windowHeight="19760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,13 +50,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -81,7 +87,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -384,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -400,7 +406,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="1">
-        <v>1500</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -408,7 +414,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1">
-        <v>750</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -416,7 +422,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="1">
-        <v>3000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -424,7 +430,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="1">
-        <v>300</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -432,7 +438,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="1">
-        <v>1500</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -440,8 +446,11 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>750</v>
-      </c>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B8" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/core_portfolio.xlsx
+++ b/core_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daivieth/Documents/_G8I/Development/IVP-Portfolio-Management-Utils/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9A8012B-3BBF-3F43-976F-4C88E6AAB88C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1AF98E3-90E5-824E-8F81-5A297A38701F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -399,7 +399,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -407,7 +407,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -415,7 +415,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -423,7 +423,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -431,7 +431,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -439,7 +439,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.66</v>
       </c>
     </row>
   </sheetData>

--- a/core_portfolio.xlsx
+++ b/core_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daivieth/Documents/_G8I/Development/IVP-Portfolio-Management-Utils/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1AF98E3-90E5-824E-8F81-5A297A38701F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FCAB1C9-1936-284F-A097-85C21A0BC0E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13620" yWindow="500" windowWidth="19980" windowHeight="19760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,35 +28,41 @@
     <t>quantity</t>
   </si>
   <si>
-    <t>ROYL.AX</t>
-  </si>
-  <si>
-    <t>UMAX.AX</t>
-  </si>
-  <si>
-    <t>YMAX.AX</t>
-  </si>
-  <si>
-    <t>VHY.AX</t>
-  </si>
-  <si>
     <t>SLF.AX</t>
   </si>
   <si>
-    <t>XGOV.AX</t>
+    <t>VAF.AX</t>
+  </si>
+  <si>
+    <t>VGB.AX</t>
+  </si>
+  <si>
+    <t>VAP.AX</t>
+  </si>
+  <si>
+    <t>VAS.AX</t>
+  </si>
+  <si>
+    <t>SEMI.AX</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -79,8 +85,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -398,48 +405,48 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
-        <v>6.7</v>
+      <c r="B2" s="1">
+        <v>911</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
-        <v>6.66</v>
+      <c r="B3" s="1">
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4">
-        <v>6.66</v>
+      <c r="B4" s="1">
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>6.66</v>
+      <c r="B5" s="1">
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6">
-        <v>6.66</v>
+      <c r="B6" s="1">
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7">
-        <v>6.66</v>
+      <c r="B7" s="1">
+        <v>470</v>
       </c>
     </row>
   </sheetData>

--- a/core_portfolio.xlsx
+++ b/core_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daivieth/Documents/_G8I/Development/IVP-Portfolio-Management-Utils/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FCAB1C9-1936-284F-A097-85C21A0BC0E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8E14613-1255-0E43-93E5-D80CCAEDA438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13620" yWindow="500" windowWidth="19980" windowHeight="19760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>ticker</t>
   </si>
@@ -31,19 +31,37 @@
     <t>SLF.AX</t>
   </si>
   <si>
-    <t>VAF.AX</t>
-  </si>
-  <si>
-    <t>VGB.AX</t>
-  </si>
-  <si>
-    <t>VAP.AX</t>
-  </si>
-  <si>
-    <t>VAS.AX</t>
-  </si>
-  <si>
-    <t>SEMI.AX</t>
+    <t>ROYL.AX</t>
+  </si>
+  <si>
+    <t>UMAX.AX</t>
+  </si>
+  <si>
+    <t>YMAX.AX</t>
+  </si>
+  <si>
+    <t>VHY.AX</t>
+  </si>
+  <si>
+    <t>XGOV.AX</t>
+  </si>
+  <si>
+    <t>CGFPC.AX</t>
+  </si>
+  <si>
+    <t>NABPF.AX</t>
+  </si>
+  <si>
+    <t>MQGPD.AX</t>
+  </si>
+  <si>
+    <t>WBCPJ.AX</t>
+  </si>
+  <si>
+    <t>CBAPJ.AX</t>
+  </si>
+  <si>
+    <t>AN3PI.AX</t>
   </si>
 </sst>
 </file>
@@ -390,7 +408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -403,42 +421,42 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1">
-        <v>911</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1">
-        <v>271</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="1">
-        <v>268</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="1">
-        <v>124</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B6" s="1">
-        <v>111</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -446,7 +464,55 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>470</v>
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1">
+        <v>3.33</v>
       </c>
     </row>
   </sheetData>
